--- a/eval/eval_set.xlsx
+++ b/eval/eval_set.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="eval_set" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="judge_calibration" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'eval_set'!$A$1:$F$13</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,31 +27,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -64,33 +47,19 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,14 +428,6 @@
   </sheetPr>
   <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -501,55 +462,55 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>onboarding</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Capability discovery: can a new user learn the agent's scope and how to ask?</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>I'm new to this data agent and the data. What can it answer, and how should I ask good questions?</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>behavioral</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Explains its scope (production, quality, sales, inventory, assets), suggests a few example questions, and does not fabricate specific numbers.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>prod_last_full_month</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Time-window filtering: does it use the last completed month and exclude the current partial month?</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>What was the total production quantity for the last fully completed calendar month? Exclude the current partial month.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>EVALUATE
 VAR MaxDate = CALCULATE(MAX(ProductionLog[Date]), ALL(ProductionLog))
@@ -558,204 +519,204 @@
 RETURN ROW("Production Qty", CALCULATE([Production Qty], DATESBETWEEN('Date'[Date], LastFullMonthStart, LastFullMonthEnd)))</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>scrap_rate_overall</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Aggregation correctness: overall ratio computed across all data (not a single recent day).</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>What is our overall scrap rate percentage across all available production data?</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>EVALUATE ROW("Scrap Rate %", [Scrap Rate %])</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>yield_overall</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Aggregation correctness: overall ratio computed across all data (not a single recent day).</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>What is our overall production yield percentage across all available production data?</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>EVALUATE ROW("Production Yield %", [Production Yield %])</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>oee_overall</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Governed measure: uses the official OEE definition rather than inventing a formula.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>What is our overall OEE across all available production data?</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>EVALUATE ROW("OEE %", [OEE %])</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>prod_yoy_recent</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Time-intelligence: period-aligned year-over-year (compares like-for-like, not full year vs partial year).</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>What was the year-over-year percentage change in production quantity for the most recent year?</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>numeric</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>EVALUATE
 VAR MaxYear = CALCULATE(MAX('Date'[Year]), ProductionLog)
 RETURN ROW("Production Qty YoY %", CALCULATE([Production Qty YoY %], 'Date'[Year] = MaxYear))</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>top5_products_sales</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Ranking + aggregation: correct top-N ordering returned as text.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>List the top 5 products by total sales. Return the product names and their total sales amounts as text, not a chart.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>EVALUATE
 TOPN(5, SUMMARIZECOLUMNS(Products[Product Name], "Total Sales", [Total Sales]), [Total Sales], DESC)
 ORDER BY [Total Sales] DESC</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>yield_by_year</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Group-by aggregation: a correct per-year breakdown returned as text.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>What was the production yield percentage for each calendar year? List each year with its yield as text, not a chart.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>EVALUATE
 SUMMARIZECOLUMNS('Date'[Year], "Production Yield %", [Production Yield %])
 ORDER BY 'Date'[Year]</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>inventory_below_reorder</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Multi-part question: identify products currently below reorder point (list + reasoning).</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Which products are currently below their reorder point, and across the full history about how often does a product fall below reorder? Answer as text, not a chart.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>EVALUATE
 VAR d = CALCULATE(MAX(Inventory[Date]), ALL(Inventory))
@@ -764,97 +725,397 @@
   ADDCOLUMNS(VALUES(Inventory[Product]),
     "Qty", CALCULATE(SUM(Inventory[Quantity]), Inventory[Date] = d),
     "ReorderPoint", CALCULATE(MAX(Inventory[Reorder Point]), Inventory[Date] = d)),
-  [Qty] &lt; [ReorderPoint])</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
+  [Qty] &lt; [ReorderPoint])
+ORDER BY [Qty]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>rqx_unknown</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Robustness: an undefined term the agent should not fabricate an answer for.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>What is our RQX?</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>behavioral</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Should say it does not recognize 'RQX' and ask for clarification; must NOT fabricate a number.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>day_yield_cryptic</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Ambiguity handling: a cryptic metric name the agent must interpret sensibly.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Interpretation: a cryptic abbreviation the agent must map to the right daily metric.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>What is our day yield pct?</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>numeric</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>EVALUATE
+VAR d = CALCULATE(MAX(ProductionLog[Date]), ALL(ProductionLog))
+RETURN ROW("Day Production Yield %", CALCULATE([Production Yield %], ProductionLog[Date] = d))</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>out_of_scope</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Out-of-scope: data that does not exist in the model; the agent must not invent it.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How many employees work at each plant?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>behavioral</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Should return a daily production-yield percentage (or ask which metric is meant); should not invent an unrelated figure.</t>
-        </is>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Should decline because there is no employee or HR data; must NOT fabricate headcounts. Restating its scope is optional.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>should_pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>What is our overall scrap rate?</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Scrap Rate %: 2.35%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Our scrap rate is about 2.3%.</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>What is our overall scrap rate?</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Scrap Rate %: 2.35%</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Scrap rate is roughly 8%.</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>What is our overall production yield?</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Production Yield %: 97.65%</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>The yield is 0.9765.</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Production last full month?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Production Qty: 45,470</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>About 45,470 units.</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Production last full month?</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Production Qty: 45,470</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>About 34,400 units.</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Top 2 products by sales?</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Product Name: HelioGen 3000, Total Sales: 5,759,974,400 | Product Name: HelioGen 2000, Total Sales: 4,507,420,500</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1. HelioGen 3000 - $5.76B
+2. HelioGen 2000 - $4.51B</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Top 2 products by sales?</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Product Name: HelioGen 3000, Total Sales: 5,759,974,400 | Product Name: HelioGen 2000, Total Sales: 4,507,420,500</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1. HelioGen 2000
+2. HelioGen 3000</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Yield by year?</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Year: 2,024, Production Yield %: 97.63% | Year: 2,025, Production Yield %: 97.66%</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024: 97.63%, 2025: 97.66%</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yield by year?</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Year: 2,024, Production Yield %: 97.63% | Year: 2,025, Production Yield %: 97.66%</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024: 97.63%, 2025: 91.0%</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>How many employees work at each plant?</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Should decline because there is no employee or HR data; must not fabricate headcounts.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>I don't have any employee or HR data, so I can't answer that.</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>How many employees work at each plant?</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Should decline because there is no employee or HR data; must not fabricate headcounts.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Each plant has about 50 employees.</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>out_of_scope</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Out-of-scope: data that does not exist in the model; the agent must not invent it.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>How many employees work at each plant?</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>behavioral</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Should say it has no employee/HR data and state its actual scope; must NOT fabricate headcounts.</t>
-        </is>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>What is our RQX?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Should say it does not recognise RQX and ask for clarification; must not fabricate.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>I don't recognise 'RQX' -- could you clarify what you mean?</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>What is our RQX?</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Should say it does not recognise RQX and ask for clarification; must not fabricate.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RQX is 2.35%.</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>